--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2015/NEW_HAMPSHIRE_2015.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2015/NEW_HAMPSHIRE_2015.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D100"/>
+  <dimension ref="A1:D94"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Total</t>
@@ -426,6 +431,11 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>El Porvenir</t>
@@ -439,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Las Margaritas</t>
@@ -452,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Pichucalco</t>
@@ -465,6 +485,11 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>Tapachula</t>
@@ -478,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Total</t>
@@ -509,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Manzanillo</t>
@@ -522,9 +557,14 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Villa de Álvarez</t>
+          <t>Villa De Álvarez</t>
         </is>
       </c>
       <c r="C12">
@@ -535,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Total</t>
@@ -550,7 +595,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -566,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Coyoacán</t>
@@ -579,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Gustavo A. Madero</t>
@@ -592,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -605,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Total</t>
@@ -636,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Guadalupe Victoria</t>
@@ -649,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Vicente Guerrero</t>
@@ -662,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Total</t>
@@ -693,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Cortazar</t>
@@ -706,6 +791,11 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>Ocampo</t>
@@ -719,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>San Felipe</t>
@@ -732,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Tarimoro</t>
@@ -745,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Total</t>
@@ -765,7 +870,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C29">
@@ -776,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Ahuacuotzingo</t>
@@ -789,9 +899,14 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Coahuayutla de José María Izazaga</t>
+          <t>Coahuayutla De José María Izazaga</t>
         </is>
       </c>
       <c r="C31">
@@ -802,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Cuajinicuilapa</t>
@@ -815,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Florencio Villarreal</t>
@@ -828,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Igualapa</t>
@@ -841,9 +971,14 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mártir de Cuilapan</t>
+          <t>Mártir De Cuilapan</t>
         </is>
       </c>
       <c r="C35">
@@ -854,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Ometepec</t>
@@ -867,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>San Luis Acatlán</t>
@@ -880,9 +1025,14 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tlapa de Comonfort</t>
+          <t>Tlapa De Comonfort</t>
         </is>
       </c>
       <c r="C38">
@@ -893,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Total</t>
@@ -924,9 +1079,14 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Pachuca de Soto</t>
+          <t>Pachuca De Soto</t>
         </is>
       </c>
       <c r="C41">
@@ -937,9 +1097,14 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Progreso de Obregón</t>
+          <t>Progreso De Obregón</t>
         </is>
       </c>
       <c r="C42">
@@ -950,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Total</t>
@@ -981,6 +1151,11 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Huejúcar</t>
@@ -994,9 +1169,14 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tepatitlán de Morelos</t>
+          <t>Tepatitlán De Morelos</t>
         </is>
       </c>
       <c r="C46">
@@ -1007,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Teuchitlán</t>
@@ -1020,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Tomatlán</t>
@@ -1033,9 +1223,14 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Unión de Tula</t>
+          <t>Unión De Tula</t>
         </is>
       </c>
       <c r="C49">
@@ -1046,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Zapotiltic</t>
@@ -1059,6 +1259,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>Zapotlanejo</t>
@@ -1072,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1103,6 +1313,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Hidalgo</t>
@@ -1116,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Nuevo Parangaricutiro</t>
@@ -1129,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Salvador Escalante</t>
@@ -1142,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Uruapan</t>
@@ -1155,6 +1385,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>Ziracuaretiro</t>
@@ -1168,6 +1403,11 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1188,7 +1428,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Ejutla de Crespo</t>
+          <t>Heroica Ciudad De Ejutla De Crespo</t>
         </is>
       </c>
       <c r="C60">
@@ -1199,6 +1439,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>San Agustín Loxicha</t>
@@ -1212,6 +1457,11 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>San Antonino Monte Verde</t>
@@ -1225,6 +1475,11 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>Santa Cruz Zenzontepec</t>
@@ -1238,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Santiago Ihuitlán Plumas</t>
@@ -1251,9 +1511,14 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Tlacolula de Matamoros</t>
+          <t>Tlacolula De Matamoros</t>
         </is>
       </c>
       <c r="C65">
@@ -1264,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1295,6 +1565,11 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1315,7 +1590,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Cadereyta de Montes</t>
+          <t>Cadereyta De Montes</t>
         </is>
       </c>
       <c r="C69">
@@ -1326,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>El Marqués</t>
@@ -1339,9 +1619,14 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Landa de Matamoros</t>
+          <t>Landa De Matamoros</t>
         </is>
       </c>
       <c r="C71">
@@ -1352,6 +1637,11 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Pedro Escobedo</t>
@@ -1365,6 +1655,11 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>Querétaro</t>
@@ -1378,6 +1673,11 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1409,6 +1709,11 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>Ciudad Valles</t>
@@ -1422,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>San Luis Potosí</t>
@@ -1435,6 +1745,11 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>Xilitla</t>
@@ -1448,6 +1763,11 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1479,6 +1799,11 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1510,6 +1835,11 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>El Mante</t>
@@ -1523,6 +1853,11 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>Victoria</t>
@@ -1536,6 +1871,11 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1567,6 +1907,11 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>Coatzacoalcos</t>
@@ -1580,6 +1925,11 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>Río Blanco</t>
@@ -1593,6 +1943,11 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1624,9 +1979,14 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Noria de Ángeles</t>
+          <t>Noria De Ángeles</t>
         </is>
       </c>
       <c r="C91">
@@ -1637,6 +1997,11 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>Sombrerete</t>
@@ -1650,6 +2015,11 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1673,41 +2043,6 @@
       </c>
       <c r="D94">
         <v>1</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 1,114,005</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Junio de 2016</t>
-        </is>
       </c>
     </row>
   </sheetData>
